--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104718_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104718_W29.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7142</v>
+        <v>6.9201</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8498</v>
+        <v>7.8172</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1356</v>
+        <v>-0.8971</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9338</v>
+        <v>4.9305</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2856</v>
+        <v>1.2839</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6482</v>
+        <v>3.6466</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8495</v>
+        <v>5.8337</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1339</v>
+        <v>3.1231</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7155</v>
+        <v>2.7106</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9157</v>
+        <v>-0.9032</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8484</v>
+        <v>-1.8392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9327</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9712</v>
+        <v>-0.7537</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2522</v>
+        <v>-0.2559</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.719</v>
+        <v>-0.4978</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4332</v>
+        <v>3.4262</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5244</v>
+        <v>4.5157</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9816</v>
+        <v>5.6112</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7962</v>
+        <v>5.1846</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1854</v>
+        <v>0.4266</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5502</v>
+        <v>3.3639</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1067</v>
+        <v>-1.1148</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6569</v>
+        <v>4.4787</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3954</v>
+        <v>4.0656</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4562</v>
+        <v>0.7822</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9392</v>
+        <v>3.2834</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8452</v>
+        <v>-0.7017</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5629</v>
+        <v>-1.897</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7177</v>
+        <v>1.1953</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0447</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0447</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005</v>
+        <v>-1.2762</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5992</v>
+        <v>-0.1282</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5997</v>
+        <v>-1.148</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3862</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3726</v>
+        <v>4.7381</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3123</v>
+        <v>2.9339</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0603</v>
+        <v>1.8042</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3663</v>
+        <v>2.5473</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1188</v>
+        <v>-1.1083</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4851</v>
+        <v>3.6556</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0838</v>
+        <v>3.378</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7897</v>
+        <v>0.4439</v>
       </c>
       <c r="L4" t="n">
-        <v>3.294</v>
+        <v>2.934</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7175</v>
+        <v>-0.8307</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9085</v>
+        <v>-1.5522</v>
       </c>
       <c r="O4" t="n">
-        <v>1.191</v>
+        <v>0.7215</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2719</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2719</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.5162</v>
+        <v>-0.2448</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0221</v>
+        <v>-0.4441</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.494</v>
+        <v>0.1992</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2507</v>
+        <v>0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2507</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3339</v>
+        <v>1.9157</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9618</v>
+        <v>2.0185</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3721</v>
+        <v>-0.1029</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3052</v>
+        <v>0.3106</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4125</v>
+        <v>-0.4109</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7177</v>
+        <v>0.7215</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1994</v>
+        <v>2.1887</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8266</v>
+        <v>1.8164</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3728</v>
+        <v>0.3724</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8942</v>
+        <v>-1.8781</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.2391</v>
+        <v>-2.2273</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3449</v>
+        <v>0.3492</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7781</v>
+        <v>0.3578</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7836</v>
+        <v>0.8589</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0055</v>
+        <v>-0.5011</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3881</v>
+        <v>1.3882</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9041</v>
+        <v>2.206</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.516</v>
+        <v>-0.8179</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4668</v>
+        <v>0.4706</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.5977</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0672</v>
+        <v>1.0683</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0021</v>
+        <v>1.0005</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2938</v>
+        <v>0.293</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7083</v>
+        <v>0.7075</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5353</v>
+        <v>-0.53</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8941</v>
+        <v>-0.8907</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3588</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0125</v>
+        <v>0.0071</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1893</v>
+        <v>0.116</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2018</v>
+        <v>-0.1089</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2116</v>
+        <v>1.0057</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1419</v>
+        <v>1.6441</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9304</v>
+        <v>-0.6384</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8332</v>
+        <v>-1.8307</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2593</v>
+        <v>-1.2555</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5739</v>
+        <v>-0.5752</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9805</v>
+        <v>-0.9865</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4778</v>
+        <v>-0.4794</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5026</v>
+        <v>-0.5071</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8527</v>
+        <v>-0.8442</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7814</v>
+        <v>-0.7761</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0712</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1378</v>
+        <v>-0.3425</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6057</v>
+        <v>-0.0931</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5321</v>
+        <v>-0.2494</v>
       </c>
       <c r="V7" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,19 +1033,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6032</v>
+        <v>-0.5063</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0801</v>
+        <v>0.2612</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6833</v>
+        <v>-0.7675</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1324</v>
+        <v>0.1339</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2637</v>
+        <v>-0.2641</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3961</v>
+        <v>0.398</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3371</v>
+        <v>0.3335</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2998</v>
+        <v>0.2963</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2047</v>
+        <v>-0.1997</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5635</v>
+        <v>-0.5604</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3588</v>
+        <v>0.3608</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.031</v>
+        <v>0.064</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4164</v>
+        <v>-0.2301</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3854</v>
+        <v>0.294</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SHACKELFORD</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5189</v>
+        <v>-1.0626</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9977</v>
+        <v>-1.4403</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5165</v>
+        <v>0.3776</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1933</v>
+        <v>-2.2417</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4584</v>
+        <v>-1.5252</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6517</v>
+        <v>-0.7165</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3447</v>
+        <v>-1.238</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7371</v>
+        <v>-0.6345</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0818</v>
+        <v>-0.6035</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1514</v>
+        <v>-1.0037</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.8907</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4301</v>
+        <v>-0.113</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.621</v>
+        <v>-0.0988</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.347</v>
+        <v>-0.2023</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2739</v>
+        <v>0.1035</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0913</v>
+        <v>-0.3155</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0913</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>J. SHACKELFORD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5819</v>
+        <v>-1.0806</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7911</v>
+        <v>1.3674</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2092</v>
+        <v>-2.448</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2445</v>
+        <v>0.1924</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5275</v>
+        <v>-1.4563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.717</v>
+        <v>1.6487</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2359</v>
+        <v>1.3397</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6334</v>
+        <v>-0.7379</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6025</v>
+        <v>2.0776</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0086</v>
+        <v>-1.1472</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8941</v>
+        <v>-0.7184</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1145</v>
+        <v>-0.4289</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5903</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5903</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6089</v>
+        <v>-0.1835</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5553</v>
+        <v>0.0278</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0537</v>
+        <v>-0.2113</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3188</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3188</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1999</v>
+        <v>-4.175</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0315</v>
+        <v>-4.1515</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1684</v>
+        <v>-0.0235</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2105</v>
+        <v>0.2133</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4839</v>
+        <v>-0.4826</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6944</v>
+        <v>0.6959</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2413</v>
+        <v>-0.248</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1659</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0806</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4518</v>
+        <v>0.4613</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3231</v>
+        <v>-0.3168</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7749</v>
+        <v>0.778</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.7709</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.6797</v>
+        <v>-5.6908</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1337</v>
+        <v>0.1628</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2526</v>
+        <v>0.1531</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1189</v>
+        <v>0.0097</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2268</v>
+        <v>0.2292</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4101</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.055999999999999</v>
+        <v>-7.3145</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8379</v>
+        <v>-3.2329</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2181</v>
+        <v>-4.0816</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.8616</v>
+        <v>-5.8579</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.0249</v>
+        <v>-3.0216</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.8367</v>
+        <v>-2.8364</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.2133</v>
+        <v>-3.2187</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9211</v>
+        <v>-0.9243</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.2921</v>
+        <v>-2.2945</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6484</v>
+        <v>-2.6392</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1038</v>
+        <v>-2.0973</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5446</v>
+        <v>-0.5419</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3303</v>
+        <v>-0.5947</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6247</v>
+        <v>-0.0141</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7056</v>
+        <v>-0.5805</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.869300000000001</v>
+        <v>7.267599999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3834</v>
+        <v>14.6082</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.5141</v>
+        <v>-7.3409</v>
       </c>
       <c r="G14" t="n">
-        <v>2.046399999999999</v>
+        <v>2.059800000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.1432</v>
+        <v>-10.1255</v>
       </c>
       <c r="I14" t="n">
-        <v>12.1897</v>
+        <v>12.1852</v>
       </c>
       <c r="J14" t="n">
-        <v>12.541</v>
+        <v>12.4485</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8699</v>
+        <v>3.8129</v>
       </c>
       <c r="L14" t="n">
-        <v>8.671100000000001</v>
+        <v>8.6355</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.4947</v>
+        <v>-10.3888</v>
       </c>
       <c r="N14" t="n">
-        <v>-14.013</v>
+        <v>-13.9385</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5184</v>
+        <v>3.5497</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2719</v>
+        <v>2.276199999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2235</v>
+        <v>-10.2434</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4953</v>
+        <v>12.5196</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.2916</v>
+        <v>-2.9025</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5757</v>
+        <v>-0.212</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7158</v>
+        <v>-2.6906</v>
       </c>
       <c r="V14" t="n">
-        <v>5.842500000000001</v>
+        <v>5.8343</v>
       </c>
       <c r="W14" t="n">
-        <v>12.6415</v>
+        <v>12.6153</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.799199999999999</v>
+        <v>-6.781000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8338</v>
+        <v>4.2499</v>
       </c>
       <c r="E15" t="n">
-        <v>6.7829</v>
+        <v>4.7328</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.4829</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3877</v>
+        <v>0.3786</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5772</v>
+        <v>3.568</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.1896</v>
+        <v>-3.1895</v>
       </c>
       <c r="J15" t="n">
-        <v>2.278</v>
+        <v>2.2526</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3211</v>
+        <v>4.3017</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.0432</v>
+        <v>-2.0491</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8903</v>
+        <v>-1.874</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7439</v>
+        <v>-0.7337</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1464</v>
+        <v>-1.1403</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1727</v>
+        <v>1.6013</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5031</v>
+        <v>1.4881</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3303</v>
+        <v>0.1132</v>
       </c>
       <c r="V15" t="n">
-        <v>2.9549</v>
+        <v>2.9529</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2738</v>
+        <v>3.2684</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1885</v>
+        <v>3.7289</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1243</v>
+        <v>2.9899</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0641</v>
+        <v>0.739</v>
       </c>
       <c r="G16" t="n">
-        <v>1.868</v>
+        <v>1.8673</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8799</v>
+        <v>2.8753</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0119</v>
+        <v>-1.008</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5658</v>
+        <v>3.5548</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8574</v>
+        <v>2.8473</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7083</v>
+        <v>0.7075</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6978</v>
+        <v>-1.6876</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0225</v>
+        <v>0.028</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8661</v>
+        <v>1.4064</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6945</v>
+        <v>0.5732</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1716</v>
+        <v>0.8331</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6237</v>
+        <v>1.3121</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6184</v>
+        <v>4.1225</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9947</v>
+        <v>-2.8104</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0854</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2427</v>
+        <v>-1.2434</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3282</v>
+        <v>1.3289</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0884</v>
+        <v>2.0742</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7017</v>
+        <v>-0.7109</v>
       </c>
       <c r="L17" t="n">
-        <v>2.7901</v>
+        <v>2.7851</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.003</v>
+        <v>-1.9886</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.541</v>
+        <v>-0.5325</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4619</v>
+        <v>-1.4562</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4705</v>
+        <v>1.1567</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4834</v>
+        <v>1.0075</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0129</v>
+        <v>0.1492</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3419</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2374</v>
+        <v>0.5064</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2184</v>
+        <v>0.012</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4558</v>
+        <v>0.4944</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.099</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0239</v>
+        <v>-1.0234</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4062</v>
+        <v>0.4025</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1578</v>
+        <v>1.1549</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7516</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5052</v>
+        <v>-0.5011</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2329</v>
+        <v>-0.2301</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2723</v>
+        <v>-0.271</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3452</v>
+        <v>-0.0779</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6247</v>
+        <v>-0.3904</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2795</v>
+        <v>0.3126</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3712</v>
+        <v>-0.3372</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4056</v>
+        <v>0.4039</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7411</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3837</v>
+        <v>0.3841</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0022</v>
+        <v>0.0028</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3815</v>
+        <v>0.3813</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6138</v>
+        <v>0.613</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5965</v>
+        <v>0.5958</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2301</v>
+        <v>-0.2289</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.015</v>
+        <v>-0.0144</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.118</v>
+        <v>-0.0871</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2082</v>
+        <v>-0.2091</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0902</v>
+        <v>0.122</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.9159</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2888</v>
+        <v>1.1587</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8428</v>
+        <v>-2.0747</v>
       </c>
       <c r="G20" t="n">
-        <v>1.859</v>
+        <v>1.8606</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7612</v>
+        <v>1.7605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0979</v>
+        <v>0.1001</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6695</v>
+        <v>2.6628</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5576</v>
+        <v>2.5511</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8104</v>
+        <v>-0.8022</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7965</v>
+        <v>-0.7906</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.014</v>
+        <v>-0.0116</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4738</v>
+        <v>0.1081</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1642</v>
+        <v>0.0439</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3096</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.3412</v>
+        <v>-3.3399</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.5449</v>
+        <v>-1.5479</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7963</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8578</v>
+        <v>-2.7805</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4562</v>
+        <v>-0.4865</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4016</v>
+        <v>-2.2939</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3193</v>
+        <v>-0.4169</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7146</v>
+        <v>1.563</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0338</v>
+        <v>-1.9799</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5568</v>
+        <v>1.702</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6169</v>
+        <v>2.4402</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1737</v>
+        <v>-0.7382</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7625</v>
+        <v>-2.1189</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0977</v>
+        <v>-0.8772</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8601</v>
+        <v>-1.2417</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5903</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2719</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6816</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0518</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3725</v>
+        <v>0.1365</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3206</v>
+        <v>0.6382</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8571</v>
+        <v>-2.9395</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7551</v>
+        <v>-2.8278</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.102</v>
+        <v>-0.1117</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4111</v>
+        <v>-1.3251</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5681</v>
+        <v>0.71</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9792</v>
+        <v>-2.0351</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7224</v>
+        <v>-0.5676</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4548</v>
+        <v>0.6098</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7323</v>
+        <v>-1.1773</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1336</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8867</v>
+        <v>0.1002</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2469</v>
+        <v>-0.8578</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0447</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4078</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.31</v>
+        <v>-0.021</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.161</v>
+        <v>0.0161</v>
       </c>
       <c r="U22" t="n">
-        <v>0.851</v>
+        <v>-0.037</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4228</v>
+        <v>-3.3092</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1431</v>
+        <v>-1.3303</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2797</v>
+        <v>-1.9789</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0488</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1255</v>
+        <v>0.1263</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1743</v>
+        <v>-2.1751</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0574</v>
+        <v>-1.0652</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2877</v>
+        <v>-0.2898</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7696</v>
+        <v>-0.7754</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9915</v>
+        <v>-0.9836</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4132</v>
+        <v>0.416</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4047</v>
+        <v>-1.3997</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9643</v>
+        <v>0.1462</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0411</v>
+        <v>-0.2164</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.3627</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6898</v>
+        <v>-4.5991</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2243</v>
+        <v>-2.5241</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4655</v>
+        <v>-2.075</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.752</v>
+        <v>-2.7463</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1676</v>
+        <v>-0.1616</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5844</v>
+        <v>-2.5847</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2353</v>
+        <v>-1.2402</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0196</v>
+        <v>1.017</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2549</v>
+        <v>-2.2572</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5167</v>
+        <v>-1.5061</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1872</v>
+        <v>-1.1786</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0059</v>
+        <v>0.079</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4669</v>
+        <v>0.2413</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.539</v>
+        <v>-0.1623</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4775</v>
+        <v>-1.4764</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.869199999999998</v>
+        <v>-5.084099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>6.4229</v>
+        <v>6.2511</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.2922</v>
+        <v>-11.3352</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.046399999999999</v>
+        <v>-2.059600000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>10.1433</v>
+        <v>10.1256</v>
       </c>
       <c r="I25" t="n">
-        <v>-12.1895</v>
+        <v>-12.1854</v>
       </c>
       <c r="J25" t="n">
-        <v>10.4946</v>
+        <v>10.3889</v>
       </c>
       <c r="K25" t="n">
-        <v>14.0131</v>
+        <v>13.9385</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.5186</v>
+        <v>-3.5495</v>
       </c>
       <c r="M25" t="n">
-        <v>-12.5411</v>
+        <v>-12.4486</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.8698</v>
+        <v>-3.8129</v>
       </c>
       <c r="O25" t="n">
-        <v>-8.671099999999999</v>
+        <v>-8.6357</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.2718</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4952</v>
+        <v>-12.5199</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2235</v>
+        <v>10.2435</v>
       </c>
       <c r="S25" t="n">
-        <v>4.291500000000001</v>
+        <v>5.0864</v>
       </c>
       <c r="T25" t="n">
-        <v>2.715799999999999</v>
+        <v>2.6907</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5759</v>
+        <v>2.3959</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.8427</v>
+        <v>-5.8344</v>
       </c>
       <c r="W25" t="n">
-        <v>5.707800000000002</v>
+        <v>5.6914</v>
       </c>
       <c r="X25" t="n">
-        <v>-11.5502</v>
+        <v>-11.5258</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104718_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104718_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.781000000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104718_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-11.5258</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
